--- a/Documents/Feuille de calculs pour la préparation des mélanges 2023-11-27.xlsx
+++ b/Documents/Feuille de calculs pour la préparation des mélanges 2023-11-27.xlsx
@@ -1,66 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lhallez\Documents\Général\Recherche\Projets\WaouWaqatali\Fabrication capteur\Documens 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djibril\Desktop\Stage_utiman\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0931D023-A5EC-484D-9CB7-A72107DE8DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Protocole pour cylindre de 40mm" sheetId="1" r:id="rId1"/>
     <sheet name="Données" sheetId="2" r:id="rId2"/>
     <sheet name="Recettes électrolyte" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>ENREGISTRER CE FICHIER POUR CHAQUE FABRICATION</t>
+  </si>
   <si>
     <t>Choix de la formulation de l'électrolyte</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>Mélanger les masses de solides suivante pour mesurées le α</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>libre</t>
     </r>
@@ -116,22 +99,20 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>Mesure du coéfficient d'expansion libre</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <b val="1"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t xml:space="preserve"> dans un tube de même diamètre que le capteur final</t>
     </r>
@@ -142,22 +123,20 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>L</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>initiale</t>
     </r>
@@ -165,32 +144,29 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>L</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t xml:space="preserve">0 </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>=</t>
     </r>
@@ -201,22 +177,20 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>Δ</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>libre</t>
     </r>
@@ -224,22 +198,20 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>L</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>finale</t>
     </r>
@@ -247,53 +219,48 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>L</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t xml:space="preserve">0 </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>+ Δ</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>libre</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t xml:space="preserve"> =</t>
     </r>
@@ -304,22 +271,20 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>α</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>libre</t>
     </r>
@@ -333,32 +298,29 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>Porosité bridé (%</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>v</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>)</t>
     </r>
@@ -369,22 +331,20 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>α</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>bridé</t>
     </r>
@@ -422,32 +382,29 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>Volume total d'électrolyte expansé (cm</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
         <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>3</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+        <color theme="1"/>
+        <scheme val="none"/>
       </rPr>
       <t>)</t>
     </r>
@@ -502,58 +459,17 @@
   </si>
   <si>
     <t>Formulation</t>
-  </si>
-  <si>
-    <t>ENREGISTRER CE FICHIER POUR CHAQUE FABRICATION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;-* #,##0.00_-;_-* -??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00 _€_-;-* #,##0.00 _€_-;_-* -?? _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,7 +481,33 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -578,7 +520,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.149998474074526"/>
         <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
@@ -612,20 +560,13 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -640,66 +581,56 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -771,14 +702,6 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -787,39 +710,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>315360</xdr:colOff>
+      <xdr:colOff>315595</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>47160</xdr:rowOff>
+      <xdr:rowOff>46990</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>780480</xdr:colOff>
+      <xdr:colOff>780415</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>52560</xdr:rowOff>
+      <xdr:rowOff>52705</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Image 1"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15750360" y="1836720"/>
-          <a:ext cx="3690720" cy="1975680"/>
+          <a:off x="15750361" y="1836720"/>
+          <a:ext cx="3690721" cy="1975681"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -831,39 +748,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>371880</xdr:colOff>
+      <xdr:colOff>372110</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>357840</xdr:colOff>
+      <xdr:colOff>358140</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135890</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Image 2"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16613280" y="3976560"/>
+          <a:off x="16613281" y="3976561"/>
           <a:ext cx="1598760" cy="1548000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
@@ -983,15 +894,15 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1044,550 +955,547 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.45313" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="50.33203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="37.21875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="50.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="46.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="50.36328" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.17969" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.36328" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46.45313" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.63281" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" ht="16.5">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C6)</f>
+        <v>7</v>
+      </c>
+      <c r="D6" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C6)</f>
         <v>25</v>
       </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:E11" ca="1" si="0">B$7*D6/100</f>
+      <c r="E6" s="2">
+        <f t="shared" ref="E6:E11" si="0">B$7*D6/100</f>
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4">
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
         <v>100</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C7)</f>
+        <v>9</v>
+      </c>
+      <c r="D7" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C7)</f>
         <v>36</v>
       </c>
-      <c r="E7" s="5">
-        <f t="shared" ca="1" si="0"/>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="6">
         <v>35</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C8)</f>
+        <v>11</v>
+      </c>
+      <c r="D8" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C8)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="5">
-        <f t="shared" ca="1" si="0"/>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B9" s="8">
         <f>B7/(PI()*4*B8/10)</f>
         <v>2.2736420441699337</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C9)</f>
+        <v>13</v>
+      </c>
+      <c r="D9" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C9)</f>
         <v>1</v>
       </c>
-      <c r="E9" s="5">
-        <f t="shared" ca="1" si="0"/>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C10)</f>
+        <v>15</v>
+      </c>
+      <c r="D10" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C10)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="5">
-        <f t="shared" ca="1" si="0"/>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C11)</f>
+        <v>16</v>
+      </c>
+      <c r="D11" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C11)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="5">
-        <f t="shared" ca="1" si="0"/>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13">
       <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="4">
-        <f ca="1">LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C12)</f>
+        <v>18</v>
+      </c>
+      <c r="D13" s="1">
+        <f>LOOKUP('Protocole pour cylindre de 40mm'!B$6,'Recettes électrolyte'!$C$5:$H$5,'Recettes électrolyte'!C12)</f>
         <v>35</v>
       </c>
-      <c r="E13" s="5">
-        <f ca="1">B$7*D13/100</f>
+      <c r="E13" s="2">
+        <f>B$7*D13/100</f>
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5" t="s">
+    <row r="15">
+      <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" ht="16.5">
+      <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4">
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1">
         <f>B8</f>
         <v>35</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="B18" s="4" t="s">
+      <c r="D17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="4">
+    </row>
+    <row r="18" ht="16.5">
+      <c r="B18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="1">
         <f>C19-C17</f>
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="4" t="s">
+    <row r="19" ht="16.5">
+      <c r="A19" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C19" s="6">
         <v>70</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5">
       <c r="A20" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <f>C18/C17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="4">
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1">
         <f>B20/(B20+1)*100</f>
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+    <row r="22">
+      <c r="A22" s="11" t="s">
         <v>30</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="24" ht="16.5">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B24" s="6">
         <v>10</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <f>(B24/100)/(1-B24/100)</f>
         <v>0.11111111111111112</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="11">
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="12">
         <f>(1-B25/B20)*100</f>
         <v>88.888888888888886</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="11">
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="12">
         <f>B25*1/(B25*1+B9)*100</f>
         <v>4.6592290218824175</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
         <v>37</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B30" s="6">
         <v>2</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="12">
+      <c r="C30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="13">
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>39</v>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B31" s="6">
         <v>0</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="12">
-        <v>125.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="C31" s="1" t="s">
         <v>41</v>
+      </c>
+      <c r="D31" s="13">
+        <v>125.59999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="B32" s="6">
         <v>0</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="12">
-        <v>69.11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="4">
+      <c r="D32" s="13">
+        <v>69.109999999999999</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5">
+      <c r="A33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="1">
         <f>B30*D30+B31*D31+B32*D32</f>
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>44</v>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="B34" s="8">
         <f>B33*(1-B24/100)</f>
-        <v>36.72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="13">
+        <v>36.719999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C36" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="36">
+      <c r="C36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="11">
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="12">
         <f>B34*B9/(1-B35/100)</f>
         <v>98.221336308141133</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="14">
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="15">
         <f>B34*B9</f>
         <v>83.488135861919957</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="15">
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="16">
         <f>B38*((B32*D32)/B33)</f>
         <v>0</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="16" t="e">
+      <c r="C39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="17" t="e">
         <f>B39/B32</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="15">
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="16">
         <f>B38*((B31*D31/B33))</f>
         <v>0</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="16" t="e">
+      <c r="C40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="17" t="e">
         <f>B40/B31</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="15">
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="16">
         <f>(B38*(B30*D30)/B33)</f>
         <v>83.488135861919957</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="16">
+      <c r="C41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="17">
         <f>B41/B30</f>
         <v>41.744067930959979</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="15">
+    <row r="42">
+      <c r="B42" s="16">
         <f>SUM(B39:B41)</f>
         <v>83.488135861919957</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="5"/>
-      <c r="C44" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="B45" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="17">
-        <f t="shared" ref="C45:C50" ca="1" si="1">B$37*D6/100</f>
+        <v>7</v>
+      </c>
+      <c r="C45" s="18">
+        <f t="shared" ref="C45:C50" si="1">B$37*D6/100</f>
         <v>24.555334077035283</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46">
       <c r="B46" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="17">
-        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C46" s="18">
+        <f t="shared" si="1"/>
         <v>35.359681070930812</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47">
       <c r="B47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="17">
-        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C47" s="18">
+        <f t="shared" si="1"/>
         <v>0.98221336308141138</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48">
       <c r="B48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="17">
-        <f t="shared" ca="1" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C48" s="18">
+        <f t="shared" si="1"/>
         <v>0.98221336308141138</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="49">
       <c r="B49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="17">
-        <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C49" s="18">
+        <f t="shared" si="1"/>
         <v>0.98221336308141138</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="50">
       <c r="B50" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="17">
-        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C50" s="18">
+        <f t="shared" si="1"/>
         <v>0.98221336308141138</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C51" s="18"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="51">
+      <c r="C51" s="19"/>
+    </row>
+    <row r="52">
       <c r="B52" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="18">
-        <f ca="1">B$37*D13/100</f>
+        <v>18</v>
+      </c>
+      <c r="C52" s="19">
+        <f>B$37*D13/100</f>
         <v>34.377467707849398</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="54">
       <c r="C54" s="8">
-        <f ca="1">SUM(C45:C52)</f>
+        <f>SUM(C45:C52)</f>
         <v>98.221336308141147</v>
       </c>
     </row>
@@ -1601,19 +1509,16 @@
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A22:E22"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118055" footer="0.5118055"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Recettes électrolyte'!$C$5:$H$5</xm:f>
           </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
           <xm:sqref>B6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
@@ -1623,180 +1528,178 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.45313" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="56.88671875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="56.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="5">
+    <row r="3" ht="14.4">
+      <c r="B3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="2">
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4">
-        <v>17.28</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
+    <row r="4" ht="14.4">
+      <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="4">
-        <v>69.11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
+      <c r="C4" s="1">
+        <v>17.280000000000001</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4">
+      <c r="B5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C5" s="1">
+        <v>69.109999999999999</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4">
+      <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="1">
         <v>66.599999999999994</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118055" footer="0.5118055"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B4:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.45313" defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="17" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="4">
+    <row r="4" ht="14.4">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+    </row>
+    <row r="5" ht="14.4">
+      <c r="B5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="1">
         <v>3</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="1">
         <v>4</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="1">
         <v>5</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" ht="14.4">
       <c r="B6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
         <v>25</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <f t="shared" ref="D6:D11" si="0">C6-1</f>
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" ht="14.4">
       <c r="B7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
         <v>36</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" ht="14.4">
       <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" ht="14.4">
       <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" ht="14.4">
       <c r="B10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" ht="14.4">
       <c r="B11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" ht="14.4">
       <c r="B12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="4">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1">
         <v>35</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="4">
+    <row r="13" ht="14.4">
+      <c r="C13" s="1">
         <f>SUM(C6:C12)</f>
         <v>100</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="1">
         <f>SUM(D6:D12)</f>
         <v>100</v>
       </c>
@@ -1805,7 +1708,7 @@
   <mergeCells count="1">
     <mergeCell ref="B4:H4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118055" footer="0.5118055"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
@@ -1822,7 +1725,7 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE02522-77FA-439A-A8A7-7BA0978B773A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/vsto/samples"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>